--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA203"/>
+  <dimension ref="A1:AA205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22517,6 +22517,212 @@
       <c r="Z203" s="2" t="inlineStr"/>
       <c r="AA203" s="2" t="inlineStr"/>
     </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Vinum Oü</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Vinum Oü</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>40193</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Harju County</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Ubalehe tee 23</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>11912</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carpevinum.ee</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>info@carpevinum.ee</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr"/>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>14102081</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carpe-vinum-veinipoed/</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CVVeinipoed</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carpevinumest/</t>
+        </is>
+      </c>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr">
+        <is>
+          <t>Kristel Nõmmik</t>
+        </is>
+      </c>
+      <c r="X204" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Sommelier</t>
+        </is>
+      </c>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristel-n%C3%B5mmik-434198ba/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Barrica Oü</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Barrica Oü</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>122361</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>3 Tallinna tänav</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>11624</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>https://barrica.ee</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>info@barrica.ee</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr"/>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>14643196</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barrica-o%C3%BC/</t>
+        </is>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barrica.veinid</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr">
+        <is>
+          <t>Margus Peek</t>
+        </is>
+      </c>
+      <c r="X205" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/margus-peek-7724a812</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA205"/>
+  <dimension ref="A1:AA207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22723,6 +22723,212 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Vinum Oü</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Vinum Oü</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>40193</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Harju County</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Ubalehe tee 23</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>11912</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carpevinum.ee</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>info@carpevinum.ee</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr"/>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>14102081</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carpe-vinum-veinipoed/</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CVVeinipoed</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carpevinumest/</t>
+        </is>
+      </c>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr">
+        <is>
+          <t>Kristel Nõmmik</t>
+        </is>
+      </c>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Sommelier</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristel-n%C3%B5mmik-434198ba/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Barrica Oü</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Barrica Oü</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>122361</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>3 Tallinna tänav</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>11624</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>https://barrica.ee</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>info@barrica.ee</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr"/>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>14643196</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barrica-o%C3%BC/</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barrica.veinid</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr">
+        <is>
+          <t>Margus Peek</t>
+        </is>
+      </c>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/margus-peek-7724a812</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA207"/>
+  <dimension ref="A1:AA211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22929,6 +22929,382 @@
         </is>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Mybooze</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Mybooze</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>45407</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>139c Pärnu maantee</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>11317</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mybooze.eu</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr"/>
+      <c r="M208" s="2" t="inlineStr"/>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>brothers@mybooze.eu</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr"/>
+      <c r="P208" s="2" t="inlineStr"/>
+      <c r="Q208" s="2" t="inlineStr"/>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mybooze/</t>
+        </is>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mybooze.eu/</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr"/>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr"/>
+      <c r="X208" s="2" t="inlineStr"/>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Jaloviini Oü</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Jaloviini Oü</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>146108</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>60a/5 Telliskivi tänav</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>10412</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>https://jaloviini.com</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>jaloviini@gmail.com</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>+44 372 501 0998</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>34594791</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr"/>
+      <c r="S209" s="2" t="inlineStr"/>
+      <c r="T209" s="2" t="inlineStr"/>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr">
+        <is>
+          <t>Kaspar-Patrik Loit</t>
+        </is>
+      </c>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Vinum Oü</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Vinum Oü</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>40193</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Harju County</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Ubalehe tee 23</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>11912</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carpevinum.ee</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>info@carpevinum.ee</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr"/>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>14102081</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carpe-vinum-veinipoed/</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CVVeinipoed</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carpevinumest/</t>
+        </is>
+      </c>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr"/>
+      <c r="W210" s="2" t="inlineStr">
+        <is>
+          <t>Kristel Nõmmik</t>
+        </is>
+      </c>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Sommelier</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristel-n%C3%B5mmik-434198ba/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Barrica Oü</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Barrica Oü</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>122361</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>3 Tallinna tänav</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>11624</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>https://barrica.ee</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>info@barrica.ee</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr"/>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>14643196</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barrica-o%C3%BC/</t>
+        </is>
+      </c>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barrica.veinid</t>
+        </is>
+      </c>
+      <c r="T211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr">
+        <is>
+          <t>Margus Peek</t>
+        </is>
+      </c>
+      <c r="X211" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y211" s="2" t="inlineStr"/>
+      <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/margus-peek-7724a812</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA211"/>
+  <dimension ref="A1:AA215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -23305,6 +23305,382 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Mybooze</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Mybooze</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>45407</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>139c Pärnu maantee</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>11317</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mybooze.eu</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr"/>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>brothers@mybooze.eu</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr"/>
+      <c r="P212" s="2" t="inlineStr"/>
+      <c r="Q212" s="2" t="inlineStr"/>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mybooze/</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mybooze.eu/</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="2" t="inlineStr"/>
+      <c r="W212" s="2" t="inlineStr"/>
+      <c r="X212" s="2" t="inlineStr"/>
+      <c r="Y212" s="2" t="inlineStr"/>
+      <c r="Z212" s="2" t="inlineStr"/>
+      <c r="AA212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Jaloviini Oü</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Jaloviini Oü</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>146108</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>60a/5 Telliskivi tänav</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>10412</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>https://jaloviini.com</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>jaloviini@gmail.com</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>+44 372 501 0998</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>34594791</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr"/>
+      <c r="S213" s="2" t="inlineStr"/>
+      <c r="T213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="inlineStr"/>
+      <c r="V213" s="2" t="inlineStr"/>
+      <c r="W213" s="2" t="inlineStr">
+        <is>
+          <t>Kaspar-Patrik Loit</t>
+        </is>
+      </c>
+      <c r="X213" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr"/>
+      <c r="AA213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Vinum Oü</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Vinum Oü</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>40193</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Harju County</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Ubalehe tee 23</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>11912</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.carpevinum.ee</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>info@carpevinum.ee</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr"/>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>14102081</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carpe-vinum-veinipoed/</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CVVeinipoed</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carpevinumest/</t>
+        </is>
+      </c>
+      <c r="U214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr">
+        <is>
+          <t>Kristel Nõmmik</t>
+        </is>
+      </c>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Sommelier</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristel-n%C3%B5mmik-434198ba/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Barrica Oü</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Barrica Oü</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>122361</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>3 Tallinna tänav</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>11624</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>https://barrica.ee</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>info@barrica.ee</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr"/>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>14643196</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barrica-o%C3%BC/</t>
+        </is>
+      </c>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barrica.veinid</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="inlineStr"/>
+      <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr">
+        <is>
+          <t>Margus Peek</t>
+        </is>
+      </c>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr"/>
+      <c r="AA215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/margus-peek-7724a812</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
